--- a/workbooks/unit-d-modeling.xlsx
+++ b/workbooks/unit-d-modeling.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,12 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -98,18 +104,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -512,10 +519,26 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>How to study one: click any cell and read its formula in the formula bar at the top of Excel. Then try changing a blue input cell (e.g. the growth rate) and watch every downstream number update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D1's model spans three tabs — Income Statement, Balance Sheet, and Cash Flow — that reference each other. Follow the green cross-sheet links to see how they connect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:F5"/>
+  <mergeCells count="3">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F7"/>
+    <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -549,100 +572,106 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>🔵 Blue text = an input assumption.   🟢 Green text = links from another tab.   Black = a formula on this sheet. This sheet is a worked example — nothing to fill in, just trace the formulas.</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>COGS % of revenue</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>OpEx % of revenue</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>D&amp;A ($000)</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Interest expense ($000)</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="11"/>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Line item ($000)</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="7" t="n">
         <v>1000</v>
       </c>
       <c r="C14">
@@ -651,7 +680,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
@@ -666,7 +695,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
@@ -681,7 +710,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Operating Expenses</t>
         </is>
@@ -696,7 +725,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
@@ -711,7 +740,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>D&amp;A</t>
         </is>
@@ -726,7 +755,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
@@ -741,7 +770,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Interest Expense</t>
         </is>
@@ -756,7 +785,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Pretax Income</t>
         </is>
@@ -771,7 +800,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
@@ -786,22 +815,23 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="5">
         <f>B22+B23</f>
         <v/>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <f>C22+C23</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -837,107 +867,113 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>🔵 Blue text = an input assumption.   🟢 Green text = links from another tab.   Black = a formula on this sheet. This sheet is a worked example — nothing to fill in, just trace the formulas.</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Beginning common stock ($000)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Beginning retained earnings ($000)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Beginning PP&amp;E, net ($000)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>AR, Inventory, AP, Debt — held flat for simplicity ($000)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>-80</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>-80</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>-250</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>-250</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Beginning cash ($000)</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="7" t="n">
         <v>170</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Plug so the implied opening balance sheet balances: (AP 80 + Debt 250 + Common Stock 300 + Retained Earnings 150) - (AR 120 + Inventory 90 + PP&amp;E 400) = 170.</t>
         </is>
@@ -946,17 +982,17 @@
     <row r="14"/>
     <row r="15"/>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Balance Sheet ($000)</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
@@ -968,11 +1004,11 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <f>'D1 Cash Flow'!B16</f>
         <v/>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="11">
         <f>'D1 Cash Flow'!C16</f>
         <v/>
       </c>
@@ -1013,26 +1049,26 @@
           <t>PP&amp;E, net</t>
         </is>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <f>$B$7-'D1 Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="11">
         <f>B20-'D1 Income Statement'!C9</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="5">
         <f>SUM(B17:B20)</f>
         <v/>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <f>SUM(C17:C20)</f>
         <v/>
       </c>
@@ -1069,16 +1105,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="5">
         <f>SUM(B23:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <f>SUM(C23:C24)</f>
         <v/>
       </c>
@@ -1105,33 +1141,33 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <f>$B$6+'D1 Income Statement'!B24</f>
         <v/>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="11">
         <f>B28+'D1 Income Statement'!C24</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="5">
         <f>B27+B28</f>
         <v/>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <f>C27+C28</f>
         <v/>
       </c>
     </row>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Check: Assets - Liab - Equity</t>
         </is>
@@ -1146,11 +1182,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="C13:F14"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="C13:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <conditionalFormatting sqref="B31:C31">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0">
@@ -1189,15 +1226,21 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>🔵 Blue text = an input assumption.   🟢 Green text = links from another tab.   Black = a formula on this sheet. This sheet is a worked example — nothing to fill in, just trace the formulas.</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Beginning cash ($000)</t>
         </is>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="11">
         <f>'D1 Balance Sheet'!B13</f>
         <v/>
       </c>
@@ -1205,17 +1248,17 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Cash Flow ($000)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
@@ -1227,11 +1270,11 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <f>'D1 Income Statement'!B24</f>
         <v/>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <f>'D1 Income Statement'!C24</f>
         <v/>
       </c>
@@ -1242,52 +1285,52 @@
           <t>Add back D&amp;A</t>
         </is>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <f>'D1 Income Statement'!B9</f>
         <v/>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <f>'D1 Income Statement'!C9</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Change in Working Capital</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>CapEx</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Net Change in Cash</t>
         </is>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <f>SUM(B9:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <f>SUM(C9:C12)</f>
         <v/>
       </c>
@@ -1309,22 +1352,23 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Ending Cash</t>
         </is>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="5">
         <f>B15+B13</f>
         <v/>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <f>C15+C13</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -1363,117 +1407,123 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>🔵 Blue text = an input assumption.   🟢 Green text = links from another tab.   Black = a formula on this sheet. This sheet is a worked example — nothing to fill in, just trace the formulas.</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Year 1 Revenue ($000)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>0.22</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>CapEx % of revenue</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.06</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="13"/>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>($000)</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
@@ -1615,28 +1665,28 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="5">
         <f>B18+B19+B20</f>
         <v/>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <f>C18+C19+C20</f>
         <v/>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <f>D18+D19+D20</f>
         <v/>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <f>E18+E19+E20</f>
         <v/>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="5">
         <f>F18+F19+F20</f>
         <v/>
       </c>
@@ -1698,7 +1748,7 @@
     </row>
     <row r="25"/>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Terminal Value (Year 5)</t>
         </is>
@@ -1709,7 +1759,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>PV of Terminal Value</t>
         </is>
@@ -1721,18 +1771,19 @@
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Enterprise Value</t>
         </is>
       </c>
-      <c r="B29" s="4">
+      <c r="B29" s="5">
         <f>SUM(B24:F24)+B27</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -1767,10 +1818,16 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>🔵 Blue text = an input assumption.   🟢 Green text = links from another tab.   Black = a formula on this sheet. This sheet is a worked example — nothing to fill in, just trace the formulas.</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Blue text</t>
         </is>
@@ -1782,7 +1839,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
@@ -1794,7 +1851,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
@@ -1807,7 +1864,7 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Example: revenue growth assumption</t>
         </is>
@@ -1819,7 +1876,7 @@
           <t>Growth rate</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -1829,7 +1886,7 @@
           <t>Prior revenue</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1846,7 +1903,7 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Example: safe division with IFERROR</t>
         </is>
@@ -1858,7 +1915,7 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1868,7 +1925,7 @@
           <t>Shares outstanding</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1893,7 +1950,8 @@
     </row>
     <row r="20"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A19:F20"/>
